--- a/docentes/González Nuñez Veronica - Estadisticos 20231.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="58">
   <si>
     <t>Mat</t>
   </si>
@@ -103,12 +103,21 @@
     <t>MARIN</t>
   </si>
   <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
+    <t>ZAVALA</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
+    <t>CERON</t>
+  </si>
+  <si>
     <t>PLIEGO</t>
   </si>
   <si>
@@ -130,12 +139,21 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
     <t>VENTURA</t>
   </si>
   <si>
+    <t>DELGADO</t>
+  </si>
+  <si>
     <t>AGUILAR</t>
   </si>
   <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
     <t>JAIRO YAIR</t>
   </si>
   <si>
@@ -160,10 +178,19 @@
     <t>ALEJANDRO</t>
   </si>
   <si>
+    <t>FERNANDA MARGARITA</t>
+  </si>
+  <si>
     <t>NIDIA GABRIELA</t>
   </si>
   <si>
+    <t>AXEL GAEL</t>
+  </si>
+  <si>
     <t>EMILIANO GERARDO</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
   </si>
 </sst>
 </file>
@@ -785,19 +812,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>33.33</v>
+        <v>72.22</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -863,7 +890,7 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -983,16 +1010,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>86.11</v>
+        <v>72.22</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1061,13 +1088,13 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>75</v>
+        <v>68.75</v>
       </c>
       <c r="H6">
         <v>7.3</v>
@@ -1106,7 +1133,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1144,10 +1171,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1167,10 +1194,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1190,10 +1217,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1213,10 +1240,10 @@
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1236,10 +1263,10 @@
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1259,10 +1286,10 @@
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1282,10 +1309,10 @@
         <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1305,10 +1332,10 @@
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1322,16 +1349,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920369</v>
+        <v>22330051920233</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1345,24 +1372,93 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920205</v>
+        <v>22330051920369</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920176</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920205</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
         <v>12</v>
       </c>
-      <c r="G11">
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920114</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20231.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -85,112 +85,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>ZAVALA</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>PALACIOS</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>IBAÑEZ</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>DELGADO</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
-  </si>
-  <si>
-    <t>JAIRO YAIR</t>
-  </si>
-  <si>
-    <t>AMALIA PAULINA</t>
-  </si>
-  <si>
-    <t>MARIA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>EVELYN ROSALIA</t>
-  </si>
-  <si>
-    <t>ELI ANTONIO</t>
-  </si>
-  <si>
-    <t>NEMESIO NAHIM</t>
+    <t>FERNANDA MARGARITA</t>
   </si>
   <si>
     <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>FERNANDA MARGARITA</t>
-  </si>
-  <si>
-    <t>NIDIA GABRIELA</t>
-  </si>
-  <si>
-    <t>AXEL GAEL</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
   </si>
 </sst>
 </file>
@@ -984,16 +894,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>86.95999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1010,13 +920,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>72.22</v>
+        <v>86.11</v>
       </c>
       <c r="H3">
         <v>7</v>
@@ -1036,16 +946,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>76.92</v>
+        <v>92.31</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1062,16 +972,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G5">
-        <v>89.29000000000001</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1088,16 +998,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>68.75</v>
+        <v>75</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1133,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1165,300 +1075,47 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920378</v>
+        <v>22330051920233</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920240</v>
+        <v>21330051920125</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920394</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920222</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920366</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920023</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920125</v>
-      </c>
-      <c r="B8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920126</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920233</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920369</v>
-      </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920176</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920205</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920114</v>
-      </c>
-      <c r="B14" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" t="s">
-        <v>57</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20231.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="34">
   <si>
     <t>Mat</t>
   </si>
@@ -85,16 +85,34 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>LLANOS</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
     <t>BONILLA</t>
   </si>
   <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>IBAÑEZ</t>
   </si>
   <si>
     <t>FLORES</t>
+  </si>
+  <si>
+    <t>SERGIO</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
   </si>
   <si>
     <t>FERNANDA MARGARITA</t>
@@ -946,13 +964,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>92.31</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H4">
         <v>7.8</v>
@@ -1043,7 +1061,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1075,16 +1093,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920233</v>
+        <v>21330051420317</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1093,21 +1111,21 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920125</v>
+        <v>21330051920126</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1116,6 +1134,52 @@
         <v>14</v>
       </c>
       <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>22330051920233</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920125</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20231.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20231.xlsx
@@ -921,7 +921,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -947,7 +947,7 @@
         <v>86.11</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -973,7 +973,7 @@
         <v>96.15000000000001</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -999,7 +999,7 @@
         <v>96.43000000000001</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1025,7 +1025,7 @@
         <v>75</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1051,7 +1051,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>8.300000000000001</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/González Nuñez Veronica - Estadisticos 20231.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20231.xlsx
@@ -921,7 +921,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -947,7 +947,7 @@
         <v>86.11</v>
       </c>
       <c r="H3">
-        <v>9.300000000000001</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -973,7 +973,7 @@
         <v>96.15000000000001</v>
       </c>
       <c r="H4">
-        <v>9.800000000000001</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -999,7 +999,7 @@
         <v>96.43000000000001</v>
       </c>
       <c r="H5">
-        <v>9.800000000000001</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1025,7 +1025,7 @@
         <v>75</v>
       </c>
       <c r="H6">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1051,7 +1051,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>
